--- a/Output/pairwise_terciles_migration_lapop.xlsx
+++ b/Output/pairwise_terciles_migration_lapop.xlsx
@@ -404,22 +404,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.220102285802277</v>
+        <v>0.220084248543764</v>
       </c>
       <c r="C2" t="n">
-        <v>0.536474321203867</v>
+        <v>0.53646069113084</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0305586782107453</v>
+        <v>0.0305541364365503</v>
       </c>
       <c r="E2" t="n">
-        <v>0.296951123404145</v>
+        <v>0.297012236291311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.433683254879653</v>
+        <v>0.433728679332275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.746073488206635</v>
+        <v>0.746071754610462</v>
       </c>
     </row>
     <row r="3">
@@ -427,22 +427,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.738366979899498</v>
+        <v>0.738377865084348</v>
       </c>
       <c r="C3" t="n">
-        <v>0.118737074851251</v>
+        <v>0.118739025086364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0252162433726075</v>
+        <v>0.0252136320834213</v>
       </c>
       <c r="E3" t="n">
-        <v>0.570251170604088</v>
+        <v>0.57030106424461</v>
       </c>
       <c r="F3" t="n">
-        <v>0.136579029043997</v>
+        <v>0.136615357346691</v>
       </c>
       <c r="G3" t="n">
-        <v>0.268539834682596</v>
+        <v>0.268578195492231</v>
       </c>
     </row>
   </sheetData>
